--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="9600"/>
+    <workbookView windowWidth="24000" windowHeight="9150"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -27,11 +27,29 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
   <si>
     <t>Client_Name</t>
   </si>
   <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Mortality</t>
+  </si>
+  <si>
+    <t>DOB</t>
+  </si>
+  <si>
+    <t>Agent</t>
+  </si>
+  <si>
+    <t>Partner</t>
+  </si>
+  <si>
+    <t>Referral</t>
+  </si>
+  <si>
     <t>Product</t>
   </si>
   <si>
@@ -72,6 +90,24 @@
   </si>
   <si>
     <t>H18 Test</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>01/01/1998</t>
+  </si>
+  <si>
+    <t>00320819</t>
+  </si>
+  <si>
+    <t>01003387</t>
+  </si>
+  <si>
+    <t>REBS</t>
   </si>
   <si>
     <t>H18</t>
@@ -718,6 +754,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1066,90 +1105,127 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:T11"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.4285714285714" customWidth="1"/>
-    <col min="5" max="5" width="10.5714285714286"/>
-    <col min="8" max="9" width="11.2857142857143" customWidth="1"/>
-    <col min="10" max="10" width="16.2857142857143" customWidth="1"/>
-    <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="4" max="4" width="11.4285714285714"/>
+    <col min="11" max="11" width="10.5714285714286"/>
+    <col min="14" max="15" width="11.2857142857143" customWidth="1"/>
+    <col min="16" max="16" width="16.2857142857143" customWidth="1"/>
+    <col min="17" max="17" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="42.75" spans="1:14">
+    <row r="1" s="1" customFormat="1" ht="42.75" spans="1:20">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:10">
+    <row r="2" s="1" customFormat="1" spans="1:16">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="1">
+        <v>23</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" s="1">
         <v>600000</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>20</v>
+      <c r="L2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1"/>
